--- a/templates/questions-template.xlsx
+++ b/templates/questions-template.xlsx
@@ -11,11 +11,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="78">
   <si>
     <t>السؤال</t>
   </si>
   <si>
+    <t>صورة السؤال</t>
+  </si>
+  <si>
     <t>أ</t>
   </si>
   <si>
@@ -55,6 +58,9 @@
     <t>جسم كتلته 2 كجم يتحرك بعجلة 3 م/ث². ما القوة المؤثرة عليه؟</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>5 نيوتن</t>
   </si>
   <si>
@@ -85,9 +91,6 @@
     <t>درس</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>وحدة قياس الشغل هي:</t>
   </si>
   <si>
@@ -212,6 +215,36 @@
   </si>
   <si>
     <t>مسائل</t>
+  </si>
+  <si>
+    <t>من الشكل: احسب طول الوتر في المثلث القائم.</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>فيثاغورس: الوتر² = 3² + 4² = 25 ← الوتر = 5</t>
+  </si>
+  <si>
+    <t>الوتر² = ضلع² + ضلع²</t>
+  </si>
+  <si>
+    <t>نظرية فيثاغورس</t>
+  </si>
+  <si>
+    <t>أي من الرسومات البيانية التالية يمثل علاقة طردية؟</t>
+  </si>
+  <si>
+    <t>العلاقة الطردية خط مستقيم يمر بنقطة الأصل</t>
+  </si>
+  <si>
+    <t>ص = ك × س</t>
+  </si>
+  <si>
+    <t>التناسب</t>
   </si>
 </sst>
 </file>
@@ -268,6 +301,206 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28000</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>119999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1524000" cy="1047750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>22000</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>89999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1047750" cy="781050"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>22000</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>89999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1047750" cy="781050"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>21999</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>89999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1047750" cy="781050"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>21999</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>89999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1047750" cy="781050"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -592,21 +825,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -646,54 +880,60 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -705,36 +945,39 @@
         <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H3" t="s">
         <v>31</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="N3" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
@@ -749,16 +992,16 @@
         <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="K4" t="s">
         <v>40</v>
@@ -769,13 +1012,16 @@
       <c r="M4" t="s">
         <v>42</v>
       </c>
+      <c r="N4" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>45</v>
@@ -787,36 +1033,39 @@
         <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="G5" t="s">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="J5" t="s">
         <v>50</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="N5" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>53</v>
@@ -828,36 +1077,39 @@
         <v>55</v>
       </c>
       <c r="F6" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="G6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" t="s">
+        <v>58</v>
+      </c>
+      <c r="L6" t="s">
         <v>24</v>
       </c>
-      <c r="H6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" t="s">
-        <v>41</v>
-      </c>
       <c r="M6" t="s">
-        <v>58</v>
+        <v>42</v>
+      </c>
+      <c r="N6" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>61</v>
@@ -869,16 +1121,16 @@
         <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
         <v>65</v>
@@ -887,14 +1139,106 @@
         <v>66</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="M7" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="N7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" t="s">
+        <v>73</v>
+      </c>
+      <c r="L8" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/templates/questions-template.xlsx
+++ b/templates/questions-template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="111">
   <si>
     <t>السؤال</t>
   </si>
@@ -55,6 +55,15 @@
     <t>سنة الامتحان</t>
   </si>
   <si>
+    <t>رقم القطعة</t>
+  </si>
+  <si>
+    <t>القطعة</t>
+  </si>
+  <si>
+    <t>صورة القطعة</t>
+  </si>
+  <si>
     <t>جسم كتلته 2 كجم يتحرك بعجلة 3 م/ث². ما القوة المؤثرة عليه؟</t>
   </si>
   <si>
@@ -245,6 +254,96 @@
   </si>
   <si>
     <t>التناسب</t>
+  </si>
+  <si>
+    <t>ما النسبة التقريبية لسطح الأرض التي يغطيها الماء؟</t>
+  </si>
+  <si>
+    <t>3%</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>71%</t>
+  </si>
+  <si>
+    <t>97%</t>
+  </si>
+  <si>
+    <t>ورد في أول القطعة أن الماء يغطي نحو 71% من سطح الأرض</t>
+  </si>
+  <si>
+    <t>لغة عربية</t>
+  </si>
+  <si>
+    <t>القراءة</t>
+  </si>
+  <si>
+    <t>فهم</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>الماء أساس الحياة على كوكب الأرض، إذ يغطي نحو 71% من سطحه. ويوجد معظم الماء في المحيطات على هيئة ماء مالح، بينما لا تتجاوز نسبة الماء العذب 3% تقريباً، يتجمد أغلبها في الأنهار الجليدية. لذلك يدعو العلماء إلى ترشيد استهلاك الماء العذب والحفاظ عليه من التلوث.</t>
+  </si>
+  <si>
+    <t>أين يتجمد أغلب الماء العذب؟</t>
+  </si>
+  <si>
+    <t>في المحيطات</t>
+  </si>
+  <si>
+    <t>في الأنهار الجليدية</t>
+  </si>
+  <si>
+    <t>في البحيرات</t>
+  </si>
+  <si>
+    <t>في المياه الجوفية</t>
+  </si>
+  <si>
+    <t>الفكرة الرئيسية للقطعة هي:</t>
+  </si>
+  <si>
+    <t>أهمية الماء وضرورة ترشيده</t>
+  </si>
+  <si>
+    <t>أنواع المحيطات</t>
+  </si>
+  <si>
+    <t>كيف تتكون الأنهار الجليدية</t>
+  </si>
+  <si>
+    <t>ملوحة مياه البحار</t>
+  </si>
+  <si>
+    <t>من الشكل: طول الضلع الأفقي يساوي:</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>من الشكل: مساحة المثلث تساوي:</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>المساحة = ½ × القاعدة × الارتفاع = ½ × 4 × 3 = 6</t>
+  </si>
+  <si>
+    <t>المساحة = ½ × ق × ع</t>
   </si>
 </sst>
 </file>
@@ -283,9 +382,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,6 +589,45 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>28000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>119999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1524000" cy="1047750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -825,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -838,402 +982,687 @@
     <col min="11" max="11" width="20" customWidth="1"/>
     <col min="12" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="60" style="1" customWidth="1"/>
+    <col min="17" max="17" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N2" t="s">
-        <v>15</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
         <v>25</v>
       </c>
-      <c r="N3" t="s">
-        <v>15</v>
-      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G5" t="s">
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N5" t="s">
-        <v>15</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G6" t="s">
         <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N6" t="s">
-        <v>59</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N7" t="s">
-        <v>15</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="P7" s="1"/>
     </row>
-    <row r="8" ht="120" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" ht="120" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N8" t="s">
-        <v>15</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="P8" s="1"/>
     </row>
-    <row r="9" ht="90" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="90" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s">
+        <v>79</v>
+      </c>
+      <c r="J9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" t="s">
+        <v>80</v>
+      </c>
+      <c r="L9" t="s">
+        <v>70</v>
+      </c>
+      <c r="M9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" t="s">
+        <v>89</v>
+      </c>
+      <c r="M10" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10" t="s">
+        <v>90</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" t="s">
+        <v>89</v>
+      </c>
+      <c r="M11" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11" t="s">
+        <v>90</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
+        <v>87</v>
+      </c>
+      <c r="K12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" t="s">
+        <v>89</v>
+      </c>
+      <c r="M12" t="s">
+        <v>28</v>
+      </c>
+      <c r="N12" t="s">
+        <v>18</v>
+      </c>
+      <c r="O12" t="s">
+        <v>90</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" t="s">
         <v>76</v>
       </c>
-      <c r="J9" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" t="s">
-        <v>77</v>
-      </c>
-      <c r="L9" t="s">
-        <v>67</v>
-      </c>
-      <c r="M9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" t="s">
-        <v>15</v>
+      <c r="L13" t="s">
+        <v>70</v>
+      </c>
+      <c r="M13" t="s">
+        <v>28</v>
+      </c>
+      <c r="N13" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13" t="s">
+        <v>105</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" t="s">
+        <v>108</v>
+      </c>
+      <c r="G14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H14" t="s">
+        <v>109</v>
+      </c>
+      <c r="I14" t="s">
+        <v>110</v>
+      </c>
+      <c r="J14" t="s">
+        <v>68</v>
+      </c>
+      <c r="K14" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M14" t="s">
+        <v>28</v>
+      </c>
+      <c r="N14" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" t="s">
+        <v>105</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
